--- a/artfynd/A 20751-2024 artfynd.xlsx
+++ b/artfynd/A 20751-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92402199</v>
+        <v>95275156</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåski, Lillström, Stöde, Mpd</t>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592761.2868338346</v>
+        <v>592884</v>
       </c>
       <c r="R2" t="n">
-        <v>6924335.646747406</v>
+        <v>6924281</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Totalt fyra blommor i nedre delen av hjärtbäcken, inte långt från vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,52 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93283770</v>
+        <v>93284255</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kåski, Lillström, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592773.3276699642</v>
+        <v>592797</v>
       </c>
       <c r="R3" t="n">
-        <v>6924336.44497495</v>
+        <v>6924334</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,12 +876,18 @@
           <t>11:03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett flertal kroppar av Rosenticka på samma granlåga.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93284255</v>
+        <v>94127374</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,41 +917,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåski, Lillström, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592797.5381437448</v>
+        <v>592797</v>
       </c>
       <c r="R4" t="n">
-        <v>6924333.412195544</v>
+        <v>6924334</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,27 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett flertal kroppar av Rosenticka på samma granlåga.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94128809</v>
+        <v>92402199</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,38 +1025,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kåski, Lillström, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592761.2868338346</v>
+        <v>592761</v>
       </c>
       <c r="R5" t="n">
-        <v>6924335.646747406</v>
+        <v>6924336</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,22 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1108,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,55 +1126,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94127196</v>
+        <v>95956042</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1594</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tricholoma atrosquamosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kåski, vid bäcken, ovanför kraftledningen , Mpd</t>
+          <t>Kåski, mellan hjärtbäcken och ravinen., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592858.4641325178</v>
+        <v>592881</v>
       </c>
       <c r="R6" t="n">
-        <v>6924311.479890219</v>
+        <v>6924295</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,15 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94127423</v>
+        <v>119848256</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,36 +1242,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kåski, Lillström, Stöde, Mpd</t>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592797.5381437448</v>
+        <v>592884</v>
       </c>
       <c r="R7" t="n">
-        <v>6924333.412195544</v>
+        <v>6924281</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,22 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,6 +1314,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1376,54 +1333,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94128773</v>
+        <v>103249592</v>
       </c>
       <c r="B8" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kåski, Lillström, Stöde, Mpd</t>
+          <t>Kåski, ravin som löper parallellt med bäcken., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592761.2868338346</v>
+        <v>592889</v>
       </c>
       <c r="R8" t="n">
-        <v>6924335.646747406</v>
+        <v>6924310</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,22 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1423,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1493,15 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94127374</v>
+        <v>96859877</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,35 +1452,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåski, Lillström, Stöde, Mpd</t>
+          <t>Hjärtbäcken, övre delen. Norra sidan ravin., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592797.5381437448</v>
+        <v>592763</v>
       </c>
       <c r="R9" t="n">
-        <v>6924333.412195544</v>
+        <v>6924344</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1564,22 +1507,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,54 +1549,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94128706</v>
+        <v>103532650</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåski, Lillström, Stöde, Mpd</t>
+          <t>Kåski, norra sidan bäcken. , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592761.2868338346</v>
+        <v>592783</v>
       </c>
       <c r="R10" t="n">
-        <v>6924335.646747406</v>
+        <v>6924353</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,22 +1615,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,7 +1644,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1723,51 +1662,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96859877</v>
+        <v>103302334</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hjärtbäcken, övre delen. Norra sidan ravin., Mpd</t>
+          <t>Kåski, ravin som löper parallellt med bäcken., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592763.3988285314</v>
+        <v>592889</v>
       </c>
       <c r="R11" t="n">
-        <v>6924343.118198099</v>
+        <v>6924310</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1794,22 +1730,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,15 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103532650</v>
+        <v>95446067</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,35 +1783,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåski, norra sidan bäcken. , Mpd</t>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592783.0633038557</v>
+        <v>592884</v>
       </c>
       <c r="R12" t="n">
-        <v>6924353.394383238</v>
+        <v>6924281</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,27 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:25</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På asp.</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,6 +1870,1698 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112333116</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>93987352</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kåski, ravin som löper parallellt med bäcken., Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592889</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6924310</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94108173</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av vårärt längs med bäcken.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94128706</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94684287</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103532791</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hjärtbäcken, Kåski. Norra sidan. , Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592893</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924290</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>94127196</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kåski, vid bäcken, ovanför kraftledningen , Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592858</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924311</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>101496507</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94108177</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94128773</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>93283770</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592774</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94128809</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111381256</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maja Lundahl, Jan-Olof Tedebrand, Kerstin Stickler, Jessica  Andersson, Margareta Byström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94108160</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>94127423</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>592797</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6924334</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>109686850</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>”Hjärtbäcken”, Lillström 107, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>592884</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6924281</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På mossig sten i bäckfåra.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20751-2024 artfynd.xlsx
+++ b/artfynd/A 20751-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95275156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93284255</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94127374</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92402199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95956042</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103249592</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859877</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103532650</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103302334</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95446067</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112333116</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2084,6 +2149,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93987352</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94108173</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128706</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94684287</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103532791</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94127196</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101496507</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2820,6 +2920,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94108177</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2922,6 +3027,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128773</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93283770</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128809</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3235,6 +3355,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111381256</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94108160</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3446,6 +3576,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94127423</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,8 +3697,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109686850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>